--- a/Projeto Organizador de Declaração de IR DIO.xlsx
+++ b/Projeto Organizador de Declaração de IR DIO.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="561" documentId="8_{351958C0-BBD9-4898-AC60-69714BC38684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3609044B-78FE-48D4-B8E2-70D1776C70D0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="0" xr2:uid="{B1AAEB88-8C21-4F2B-8818-C4968DDCCFDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="0" firstSheet="2" activeTab="2" xr2:uid="{B1AAEB88-8C21-4F2B-8818-C4968DDCCFDB}"/>
   </bookViews>
   <sheets>
     <sheet name="TÍTULAR" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
     <numFmt numFmtId="166" formatCode="&quot;(&quot;00&quot;) &quot;0000&quot;-&quot;0000"/>
     <numFmt numFmtId="167" formatCode="&quot;(&quot;00&quot;) &quot;00000&quot;-&quot;0000"/>
     <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="169" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -522,7 +522,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyBorder="1"/>
@@ -561,6 +561,46 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -579,53 +619,8 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3150,16 +3145,16 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
@@ -3311,16 +3306,16 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="6" spans="3:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" s="9" t="s">
@@ -3328,17 +3323,17 @@
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="16">
+      <c r="C7" s="27">
         <f>SUM(D12,D17,D22)</f>
         <v>536500</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C10" s="13" t="s">
@@ -3461,112 +3456,109 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="3:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="27">
+      <c r="C9" s="19">
         <v>46300</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="20">
         <v>3000</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="31"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="28"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="31"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="28"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="31"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="28"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="31"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="28"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="32"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="28"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="31"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="28"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="31"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="28"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="31"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="28"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="31"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="28"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="20"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="32"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="28"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="31"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="28"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="20"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="20"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="33"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="20"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="20"/>
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
